--- a/sales_order_forms/032_shannon_s_mani_of_the_month--sales_order_forms.xlsx
+++ b/sales_order_forms/032_shannon_s_mani_of_the_month--sales_order_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -437,12 +437,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E29"/>
+  <dimension ref="A1:E15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
-    <col width="18" customWidth="1" min="2" max="2"/>
-    <col width="18" customWidth="1" min="3" max="3"/>
+    <col width="21" customWidth="1" min="2" max="2"/>
+    <col width="24" customWidth="1" min="3" max="3"/>
     <col width="6" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
@@ -515,17 +515,17 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>date</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>order_date</t>
+          <t>order_details</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Order Date</t>
+          <t>Order Details</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
@@ -543,12 +543,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>customer_name</t>
+          <t>customer_info</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>customer name</t>
+          <t>Customer Information</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
@@ -561,23 +561,23 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>product_name</t>
+          <t>order_status</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>product name</t>
+          <t>Order Status</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -589,12 +589,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>quantity</t>
+          <t>additional_info</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>quantity</t>
+          <t>Additional Information</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
@@ -612,12 +612,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>customer_email</t>
+          <t>product_info</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>customer email</t>
+          <t>Product Information</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
@@ -635,12 +635,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>customer_phone</t>
+          <t>repeated_questions</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>customer phone</t>
+          <t>Repeated Questions</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
@@ -653,17 +653,17 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>note</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>customer_address</t>
+          <t>order_comments</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>customer address</t>
+          <t>Order Comments</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
@@ -676,17 +676,17 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>note</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>order_comments</t>
+          <t>sales_rep</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>order comments</t>
+          <t>Sales Rep</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
@@ -699,17 +699,17 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>customer_company</t>
+          <t>existing_customer</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>customer company</t>
+          <t>Existing Customer</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
@@ -727,12 +727,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>order_status</t>
+          <t>order_status_2</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>order status</t>
+          <t>Order Status 2</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
@@ -750,12 +750,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>customer_rep</t>
+          <t>sales_rep_2</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>customer rep</t>
+          <t>Sales Rep 2</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
@@ -773,338 +773,16 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>customer_type</t>
+          <t>existing_customer_2</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>customer type</t>
+          <t>Existing Customer 2</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
       <c r="E15" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>note</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>customer_notes</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>customer notes</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr"/>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>customer_type</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>customer type_</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr"/>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>customer_rep</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>customer rep_</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr"/>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>customer_address</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>customer address</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr"/>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>date</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>order_date</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>order date</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr"/>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>customer_name</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>customer name</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr"/>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>product_name</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>product name</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr"/>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>quantity</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>quantity</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr"/>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>customer_email</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>customer email</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr"/>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>customer_phone</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>customer phone</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr"/>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>customer_address</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>customer address</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr"/>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>note</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>order_comments</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>order comments</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr"/>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>customer_company</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>customer company</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr"/>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>order_status</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>order status</t>
-        </is>
-      </c>
-      <c r="D29" t="inlineStr"/>
-      <c r="E29" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -1124,9 +802,9 @@
   <dimension ref="A1:C17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="23" customWidth="1" min="1" max="1"/>
-    <col width="24" customWidth="1" min="2" max="2"/>
-    <col width="24" customWidth="1" min="3" max="3"/>
+    <col width="29" customWidth="1" min="1" max="1"/>
+    <col width="11" customWidth="1" min="2" max="2"/>
+    <col width="11" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1154,12 +832,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'value':_'pending'}</t>
+          <t>pending</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'value': 'Pending'}</t>
+          <t>Pending</t>
         </is>
       </c>
     </row>
@@ -1171,12 +849,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'value':_'shipped'}</t>
+          <t>shipped</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'value': 'Shipped'}</t>
+          <t>Shipped</t>
         </is>
       </c>
     </row>
@@ -1188,233 +866,233 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'value':_'cancelled'}</t>
+          <t>cancelled</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'value': 'Cancelled'}</t>
+          <t>Cancelled</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>customer_rep_choices</t>
+          <t>sales_rep_choices</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'value':_'sales'}</t>
+          <t>sales</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'value': 'Sales'}</t>
+          <t>Sales</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>customer_rep_choices</t>
+          <t>sales_rep_choices</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'value':_'support'}</t>
+          <t>support</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'value': 'Support'}</t>
+          <t>Support</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>customer_rep_choices</t>
+          <t>sales_rep_choices</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'value':_'marketing'}</t>
+          <t>marketing</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'value': 'Marketing'}</t>
+          <t>Marketing</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>customer_type_choices</t>
+          <t>existing_customer_choices</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'value':_'new'}</t>
+          <t>new</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'value': 'New'}</t>
+          <t>New</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>customer_type_choices</t>
+          <t>existing_customer_choices</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'value':_'existing'}</t>
+          <t>existing</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'value': 'Existing'}</t>
+          <t>Existing</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>customer_type_choices</t>
+          <t>order_status_2_choices</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'value':_'new'}</t>
+          <t>pending</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'value': 'New'}</t>
+          <t>Pending</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>customer_type_choices</t>
+          <t>order_status_2_choices</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'value':_'existing'}</t>
+          <t>shipped</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'value': 'Existing'}</t>
+          <t>Shipped</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>customer_rep_choices</t>
+          <t>order_status_2_choices</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'value':_'sales'}</t>
+          <t>cancelled</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'value': 'Sales'}</t>
+          <t>Cancelled</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>customer_rep_choices</t>
+          <t>sales_rep_2_choices</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'value':_'support'}</t>
+          <t>sales</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'value': 'Support'}</t>
+          <t>Sales</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>customer_rep_choices</t>
+          <t>sales_rep_2_choices</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'value':_'marketing'}</t>
+          <t>support</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'value': 'Marketing'}</t>
+          <t>Support</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>order_status_choices</t>
+          <t>sales_rep_2_choices</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'value':_'pending'}</t>
+          <t>marketing</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'value': 'Pending'}</t>
+          <t>Marketing</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>order_status_choices</t>
+          <t>existing_customer_2_choices</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'value':_'shipped'}</t>
+          <t>new</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'value': 'Shipped'}</t>
+          <t>New</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>order_status_choices</t>
+          <t>existing_customer_2_choices</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'value':_'cancelled'}</t>
+          <t>existing</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'value': 'Cancelled'}</t>
+          <t>Existing</t>
         </is>
       </c>
     </row>
